--- a/Presupuesto de Proyecto.xlsx
+++ b/Presupuesto de Proyecto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crfeg\OneDrive - Universidad Libre\Documentos\Universidad Libre\Septimo semestre\Gestion de proyectos\Primer corte\Documentos proyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unilibrebog-my.sharepoint.com/personal/juand-martinezo_unilibre_edu_co/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E71BE904-23E3-4D3F-989B-5331C7E1D781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30AFE141-CFAC-46CE-9E23-296589C1BB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presupuesto del proyecto" sheetId="6" r:id="rId1"/>
@@ -343,7 +343,7 @@
     <t>Definir los límites, capacidades técnicas y funcionalidades clave que abarcará el proyecto.</t>
   </si>
   <si>
-    <t>En Progreso</t>
+    <t>En Espera</t>
   </si>
   <si>
     <t>E02,E08</t>
@@ -754,6 +754,9 @@
     <t>Media</t>
   </si>
   <si>
+    <t>En Progreso</t>
+  </si>
+  <si>
     <t>Alta</t>
   </si>
   <si>
@@ -764,9 +767,6 @@
   </si>
   <si>
     <t>Atrasado</t>
-  </si>
-  <si>
-    <t>En Espera</t>
   </si>
 </sst>
 </file>
@@ -774,17 +774,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="mm/dd/yy;@"/>
-    <numFmt numFmtId="170" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="0.0%"/>
-    <numFmt numFmtId="172" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -963,7 +963,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1569,7 +1568,7 @@
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1579,11 +1578,11 @@
   </cellStyleXfs>
   <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="7" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1596,7 +1595,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1611,18 +1610,18 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="7" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
@@ -1644,7 +1643,7 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1693,51 +1692,51 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="7" fontId="11" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="5" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="7" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="5" fontId="11" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="5" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1747,7 +1746,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1756,13 +1755,13 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1780,26 +1779,26 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="5" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="5" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="6" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="7" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1823,7 +1822,7 @@
     <xf numFmtId="3" fontId="19" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1835,13 +1834,13 @@
     <xf numFmtId="3" fontId="19" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="21" fillId="22" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="22" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="22" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1850,14 +1849,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
@@ -1868,7 +1867,7 @@
     <xf numFmtId="3" fontId="19" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1877,7 +1876,7 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1887,24 +1886,24 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="7" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="25" fillId="7" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="7" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="26" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1916,29 +1915,28 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="5" fontId="4" fillId="4" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="7" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1981,12 +1979,13 @@
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Hipervínculo visitado" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="3" builtinId="9" hidden="1"/>
     <cellStyle name="Hipervínculo visitado" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Hipervínculo visitado" xfId="5" builtinId="9" hidden="1"/>
-    <cellStyle name="Hipervínculo visitado" xfId="3" builtinId="9" hidden="1"/>
     <cellStyle name="Hipervínculo visitado" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2594,30 +2593,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ436"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.15"/>
   <cols>
-    <col min="1" max="1" width="3.08203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="59.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.08203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="59.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.25" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.75" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.75" style="4" customWidth="1"/>
     <col min="12" max="12" width="8.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.375" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.83203125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="21.875" style="4" customWidth="1"/>
     <col min="16" max="16" width="8.5" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.83203125" style="4" customWidth="1"/>
+    <col min="18" max="18" width="11.875" style="4" customWidth="1"/>
     <col min="19" max="19" width="12.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.08203125" style="4" customWidth="1"/>
+    <col min="20" max="20" width="11.5" style="4" customWidth="1"/>
+    <col min="21" max="21" width="21.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.125" style="4" customWidth="1"/>
     <col min="23" max="23" width="11" style="4"/>
     <col min="24" max="24" width="4.75" style="4" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="13.75" style="4" bestFit="1" customWidth="1"/>
@@ -2626,7 +2625,7 @@
     <col min="28" max="16384" width="11" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:43" ht="45" customHeight="1" thickBot="1">
       <c r="A1" s="3"/>
       <c r="B1" s="34" t="s">
         <v>0</v>
@@ -2668,7 +2667,7 @@
       <c r="AK1" s="3"/>
       <c r="AL1" s="3"/>
     </row>
-    <row r="2" spans="1:43" s="9" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" s="9" customFormat="1" ht="35.1" customHeight="1">
       <c r="A2" s="8"/>
       <c r="B2" s="39" t="s">
         <v>1</v>
@@ -2678,28 +2677,28 @@
       <c r="E2" s="39"/>
       <c r="F2" s="39"/>
       <c r="G2" s="54"/>
-      <c r="H2" s="127" t="s">
+      <c r="H2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="125" t="s">
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="125" t="s">
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="126"/>
-      <c r="Q2" s="126"/>
-      <c r="R2" s="128"/>
-      <c r="S2" s="130" t="s">
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="126"/>
-      <c r="U2" s="131"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="130"/>
       <c r="V2" s="8"/>
       <c r="W2" s="8"/>
       <c r="X2" s="8"/>
@@ -2718,7 +2717,7 @@
       <c r="AK2" s="8"/>
       <c r="AL2" s="8"/>
     </row>
-    <row r="3" spans="1:43" s="9" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" s="9" customFormat="1" ht="35.1" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="35" t="s">
         <v>6</v>
@@ -2806,7 +2805,7 @@
       <c r="AK3" s="8"/>
       <c r="AL3" s="8"/>
     </row>
-    <row r="4" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="36" t="s">
         <v>30</v>
@@ -2863,7 +2862,7 @@
       <c r="AP4" s="8"/>
       <c r="AQ4" s="8"/>
     </row>
-    <row r="5" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="84" t="s">
         <v>33</v>
@@ -2956,7 +2955,7 @@
       <c r="AJ5" s="8"/>
       <c r="AK5" s="8"/>
     </row>
-    <row r="6" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="85" t="s">
         <v>40</v>
@@ -3049,7 +3048,7 @@
       <c r="AJ6" s="8"/>
       <c r="AK6" s="8"/>
     </row>
-    <row r="7" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" s="85" t="s">
         <v>45</v>
@@ -3136,7 +3135,7 @@
       <c r="AJ7" s="8"/>
       <c r="AK7" s="8"/>
     </row>
-    <row r="8" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="85" t="s">
         <v>50</v>
@@ -3228,7 +3227,7 @@
       <c r="AJ8" s="8"/>
       <c r="AK8" s="8"/>
     </row>
-    <row r="9" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="85" t="s">
         <v>55</v>
@@ -3321,7 +3320,7 @@
       <c r="AJ9" s="8"/>
       <c r="AK9" s="8"/>
     </row>
-    <row r="10" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="85" t="s">
         <v>61</v>
@@ -3386,7 +3385,7 @@
       <c r="X10" s="123" t="s">
         <v>63</v>
       </c>
-      <c r="Y10" s="124"/>
+      <c r="Y10" s="138"/>
       <c r="Z10" s="82">
         <f>SUM(Z4:Z9)</f>
         <v>84073429</v>
@@ -3406,7 +3405,7 @@
       <c r="AJ10" s="8"/>
       <c r="AK10" s="8"/>
     </row>
-    <row r="11" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="85" t="s">
         <v>64</v>
@@ -3485,7 +3484,7 @@
       <c r="AJ11" s="8"/>
       <c r="AK11" s="8"/>
     </row>
-    <row r="12" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="85" t="s">
         <v>66</v>
@@ -3564,7 +3563,7 @@
       <c r="AJ12" s="8"/>
       <c r="AK12" s="8"/>
     </row>
-    <row r="13" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="85" t="s">
         <v>68</v>
@@ -3643,7 +3642,7 @@
       <c r="AJ13" s="8"/>
       <c r="AK13" s="8"/>
     </row>
-    <row r="14" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="85" t="s">
         <v>71</v>
@@ -3722,7 +3721,7 @@
       <c r="AJ14" s="8"/>
       <c r="AK14" s="8"/>
     </row>
-    <row r="15" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A15" s="8"/>
       <c r="B15" s="85" t="s">
         <v>73</v>
@@ -3801,7 +3800,7 @@
       <c r="AJ15" s="8"/>
       <c r="AK15" s="8"/>
     </row>
-    <row r="16" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="85" t="s">
         <v>76</v>
@@ -3880,7 +3879,7 @@
       <c r="AJ16" s="8"/>
       <c r="AK16" s="8"/>
     </row>
-    <row r="17" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="85" t="s">
         <v>78</v>
@@ -3959,7 +3958,7 @@
       <c r="AJ17" s="8"/>
       <c r="AK17" s="8"/>
     </row>
-    <row r="18" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="85" t="s">
         <v>80</v>
@@ -4038,7 +4037,7 @@
       <c r="AJ18" s="8"/>
       <c r="AK18" s="8"/>
     </row>
-    <row r="19" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="85" t="s">
         <v>82</v>
@@ -4111,7 +4110,7 @@
       <c r="AJ19" s="8"/>
       <c r="AK19" s="8"/>
     </row>
-    <row r="20" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="85" t="s">
         <v>84</v>
@@ -4190,7 +4189,7 @@
       <c r="AP20" s="8"/>
       <c r="AQ20" s="8"/>
     </row>
-    <row r="21" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="85" t="s">
         <v>86</v>
@@ -4269,7 +4268,7 @@
       <c r="AP21" s="8"/>
       <c r="AQ21" s="8"/>
     </row>
-    <row r="22" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="85" t="s">
         <v>88</v>
@@ -4354,7 +4353,7 @@
       <c r="AP22" s="8"/>
       <c r="AQ22" s="8"/>
     </row>
-    <row r="23" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="85" t="s">
         <v>91</v>
@@ -4439,7 +4438,7 @@
       <c r="AP23" s="8"/>
       <c r="AQ23" s="8"/>
     </row>
-    <row r="24" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="85" t="s">
         <v>94</v>
@@ -4523,7 +4522,7 @@
       <c r="AP24" s="8"/>
       <c r="AQ24" s="8"/>
     </row>
-    <row r="25" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="85" t="s">
         <v>98</v>
@@ -4534,7 +4533,9 @@
       <c r="D25" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="41"/>
+      <c r="E25" s="41">
+        <v>46267</v>
+      </c>
       <c r="F25" s="86"/>
       <c r="G25" s="86"/>
       <c r="H25" s="64">
@@ -4588,7 +4589,7 @@
       <c r="AP25" s="8"/>
       <c r="AQ25" s="8"/>
     </row>
-    <row r="26" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="85" t="s">
         <v>101</v>
@@ -4599,7 +4600,9 @@
       <c r="D26" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="41"/>
+      <c r="E26" s="41">
+        <v>46273</v>
+      </c>
       <c r="F26" s="86"/>
       <c r="G26" s="86"/>
       <c r="H26" s="64">
@@ -4653,7 +4656,7 @@
       <c r="AP26" s="8"/>
       <c r="AQ26" s="8"/>
     </row>
-    <row r="27" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="85" t="s">
         <v>103</v>
@@ -4664,7 +4667,9 @@
       <c r="D27" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E27" s="41"/>
+      <c r="E27" s="41">
+        <v>46273</v>
+      </c>
       <c r="F27" s="86"/>
       <c r="G27" s="86"/>
       <c r="H27" s="64">
@@ -4718,7 +4723,7 @@
       <c r="AP27" s="8"/>
       <c r="AQ27" s="8"/>
     </row>
-    <row r="28" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="85" t="s">
         <v>105</v>
@@ -4729,7 +4734,9 @@
       <c r="D28" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="41"/>
+      <c r="E28" s="41">
+        <v>46273</v>
+      </c>
       <c r="F28" s="86"/>
       <c r="G28" s="86"/>
       <c r="H28" s="64">
@@ -4783,7 +4790,7 @@
       <c r="AP28" s="8"/>
       <c r="AQ28" s="8"/>
     </row>
-    <row r="29" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="84" t="s">
         <v>107</v>
@@ -4794,7 +4801,9 @@
       <c r="D29" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E29" s="41"/>
+      <c r="E29" s="41">
+        <v>46273</v>
+      </c>
       <c r="F29" s="86"/>
       <c r="G29" s="86"/>
       <c r="H29" s="64">
@@ -4848,7 +4857,7 @@
       <c r="AP29" s="8"/>
       <c r="AQ29" s="8"/>
     </row>
-    <row r="30" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="85" t="s">
         <v>109</v>
@@ -4859,7 +4868,9 @@
       <c r="D30" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E30" s="41"/>
+      <c r="E30" s="41">
+        <v>46280</v>
+      </c>
       <c r="F30" s="86"/>
       <c r="G30" s="86"/>
       <c r="H30" s="64">
@@ -4913,7 +4924,7 @@
       <c r="AP30" s="8"/>
       <c r="AQ30" s="8"/>
     </row>
-    <row r="31" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="85" t="s">
         <v>111</v>
@@ -4924,7 +4935,9 @@
       <c r="D31" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="41"/>
+      <c r="E31" s="41">
+        <v>46300</v>
+      </c>
       <c r="F31" s="86"/>
       <c r="G31" s="86"/>
       <c r="H31" s="64">
@@ -4978,7 +4991,7 @@
       <c r="AP31" s="8"/>
       <c r="AQ31" s="8"/>
     </row>
-    <row r="32" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="85" t="s">
         <v>113</v>
@@ -4989,7 +5002,9 @@
       <c r="D32" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="41"/>
+      <c r="E32" s="41">
+        <v>46280</v>
+      </c>
       <c r="F32" s="86"/>
       <c r="G32" s="86"/>
       <c r="H32" s="64">
@@ -5043,7 +5058,7 @@
       <c r="AP32" s="8"/>
       <c r="AQ32" s="8"/>
     </row>
-    <row r="33" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="85" t="s">
         <v>115</v>
@@ -5054,7 +5069,9 @@
       <c r="D33" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E33" s="41"/>
+      <c r="E33" s="41">
+        <v>46287</v>
+      </c>
       <c r="F33" s="86"/>
       <c r="G33" s="86"/>
       <c r="H33" s="64">
@@ -5108,7 +5125,7 @@
       <c r="AP33" s="8"/>
       <c r="AQ33" s="8"/>
     </row>
-    <row r="34" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="85" t="s">
         <v>117</v>
@@ -5119,7 +5136,9 @@
       <c r="D34" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="41"/>
+      <c r="E34" s="41">
+        <v>46306</v>
+      </c>
       <c r="F34" s="86"/>
       <c r="G34" s="86"/>
       <c r="H34" s="64">
@@ -5173,7 +5192,7 @@
       <c r="AP34" s="8"/>
       <c r="AQ34" s="8"/>
     </row>
-    <row r="35" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="84" t="s">
         <v>119</v>
@@ -5184,7 +5203,9 @@
       <c r="D35" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E35" s="41"/>
+      <c r="E35" s="41">
+        <v>46313</v>
+      </c>
       <c r="F35" s="86"/>
       <c r="G35" s="86"/>
       <c r="H35" s="64">
@@ -5238,7 +5259,7 @@
       <c r="AP35" s="8"/>
       <c r="AQ35" s="8"/>
     </row>
-    <row r="36" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="85" t="s">
         <v>121</v>
@@ -5249,7 +5270,9 @@
       <c r="D36" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E36" s="41"/>
+      <c r="E36" s="41">
+        <v>46313</v>
+      </c>
       <c r="F36" s="86"/>
       <c r="G36" s="86"/>
       <c r="H36" s="64">
@@ -5303,7 +5326,7 @@
       <c r="AP36" s="8"/>
       <c r="AQ36" s="8"/>
     </row>
-    <row r="37" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="85" t="s">
         <v>123</v>
@@ -5314,7 +5337,9 @@
       <c r="D37" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="41"/>
+      <c r="E37" s="41">
+        <v>46320</v>
+      </c>
       <c r="F37" s="86"/>
       <c r="G37" s="86"/>
       <c r="H37" s="64">
@@ -5368,7 +5393,7 @@
       <c r="AP37" s="8"/>
       <c r="AQ37" s="8"/>
     </row>
-    <row r="38" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="85" t="s">
         <v>125</v>
@@ -5379,7 +5404,9 @@
       <c r="D38" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E38" s="41"/>
+      <c r="E38" s="41">
+        <v>46320</v>
+      </c>
       <c r="F38" s="86"/>
       <c r="G38" s="86"/>
       <c r="H38" s="64">
@@ -5433,7 +5460,7 @@
       <c r="AP38" s="8"/>
       <c r="AQ38" s="8"/>
     </row>
-    <row r="39" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="85" t="s">
         <v>127</v>
@@ -5444,7 +5471,9 @@
       <c r="D39" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E39" s="41"/>
+      <c r="E39" s="41">
+        <v>46320</v>
+      </c>
       <c r="F39" s="86"/>
       <c r="G39" s="86"/>
       <c r="H39" s="64">
@@ -5498,7 +5527,7 @@
       <c r="AP39" s="8"/>
       <c r="AQ39" s="8"/>
     </row>
-    <row r="40" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="85" t="s">
         <v>129</v>
@@ -5509,7 +5538,9 @@
       <c r="D40" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="41"/>
+      <c r="E40" s="41">
+        <v>46320</v>
+      </c>
       <c r="F40" s="86"/>
       <c r="G40" s="86"/>
       <c r="H40" s="64">
@@ -5563,7 +5594,7 @@
       <c r="AP40" s="8"/>
       <c r="AQ40" s="8"/>
     </row>
-    <row r="41" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="85" t="s">
         <v>131</v>
@@ -5574,7 +5605,9 @@
       <c r="D41" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E41" s="41"/>
+      <c r="E41" s="41">
+        <v>46326</v>
+      </c>
       <c r="F41" s="86"/>
       <c r="G41" s="86"/>
       <c r="H41" s="64">
@@ -5628,7 +5661,7 @@
       <c r="AP41" s="8"/>
       <c r="AQ41" s="8"/>
     </row>
-    <row r="42" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="85" t="s">
         <v>133</v>
@@ -5639,7 +5672,9 @@
       <c r="D42" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E42" s="41"/>
+      <c r="E42" s="41">
+        <v>46326</v>
+      </c>
       <c r="F42" s="86"/>
       <c r="G42" s="86"/>
       <c r="H42" s="64">
@@ -5693,7 +5728,7 @@
       <c r="AP42" s="8"/>
       <c r="AQ42" s="8"/>
     </row>
-    <row r="43" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A43" s="8"/>
       <c r="B43" s="85" t="s">
         <v>135</v>
@@ -5704,7 +5739,9 @@
       <c r="D43" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="41"/>
+      <c r="E43" s="41">
+        <v>46333</v>
+      </c>
       <c r="F43" s="86"/>
       <c r="G43" s="86"/>
       <c r="H43" s="64">
@@ -5758,7 +5795,7 @@
       <c r="AP43" s="8"/>
       <c r="AQ43" s="8"/>
     </row>
-    <row r="44" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="85" t="s">
         <v>137</v>
@@ -5769,7 +5806,9 @@
       <c r="D44" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E44" s="41"/>
+      <c r="E44" s="41">
+        <v>46333</v>
+      </c>
       <c r="F44" s="86"/>
       <c r="G44" s="86"/>
       <c r="H44" s="64">
@@ -5827,7 +5866,7 @@
       <c r="AP44" s="8"/>
       <c r="AQ44" s="8"/>
     </row>
-    <row r="45" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="85" t="s">
         <v>139</v>
@@ -5838,7 +5877,9 @@
       <c r="D45" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E45" s="41"/>
+      <c r="E45" s="41">
+        <v>46339</v>
+      </c>
       <c r="F45" s="86"/>
       <c r="G45" s="86"/>
       <c r="H45" s="64">
@@ -5896,7 +5937,7 @@
       <c r="AP45" s="8"/>
       <c r="AQ45" s="8"/>
     </row>
-    <row r="46" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" s="9" customFormat="1" ht="30" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="20" t="s">
         <v>141</v>
@@ -5967,7 +6008,7 @@
       <c r="AP46" s="8"/>
       <c r="AQ46" s="8"/>
     </row>
-    <row r="47" spans="1:43" s="9" customFormat="1" ht="11.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" s="9" customFormat="1" ht="11.1" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
@@ -6012,7 +6053,7 @@
       <c r="AP47" s="8"/>
       <c r="AQ47" s="8"/>
     </row>
-    <row r="48" spans="1:43" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" s="3" customFormat="1" ht="21" customHeight="1">
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -6039,7 +6080,7 @@
         <v>82433368.640000001</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -6084,7 +6125,7 @@
       <c r="AP49" s="3"/>
       <c r="AQ49" s="3"/>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -6129,7 +6170,7 @@
       <c r="AP50" s="3"/>
       <c r="AQ50" s="3"/>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -6174,7 +6215,7 @@
       <c r="AP51" s="3"/>
       <c r="AQ51" s="3"/>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -6219,7 +6260,7 @@
       <c r="AP52" s="3"/>
       <c r="AQ52" s="3"/>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -6264,7 +6305,7 @@
       <c r="AP53" s="3"/>
       <c r="AQ53" s="3"/>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -6309,7 +6350,7 @@
       <c r="AP54" s="3"/>
       <c r="AQ54" s="3"/>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -6354,7 +6395,7 @@
       <c r="AP55" s="3"/>
       <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -6399,7 +6440,7 @@
       <c r="AP56" s="3"/>
       <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -6444,7 +6485,7 @@
       <c r="AP57" s="3"/>
       <c r="AQ57" s="3"/>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -6489,7 +6530,7 @@
       <c r="AP58" s="3"/>
       <c r="AQ58" s="3"/>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -6534,7 +6575,7 @@
       <c r="AP59" s="3"/>
       <c r="AQ59" s="3"/>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -6579,7 +6620,7 @@
       <c r="AP60" s="3"/>
       <c r="AQ60" s="3"/>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -6624,7 +6665,7 @@
       <c r="AP61" s="3"/>
       <c r="AQ61" s="3"/>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -6669,7 +6710,7 @@
       <c r="AP62" s="3"/>
       <c r="AQ62" s="3"/>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -6714,7 +6755,7 @@
       <c r="AP63" s="3"/>
       <c r="AQ63" s="3"/>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -6759,7 +6800,7 @@
       <c r="AP64" s="3"/>
       <c r="AQ64" s="3"/>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -6804,7 +6845,7 @@
       <c r="AP65" s="3"/>
       <c r="AQ65" s="3"/>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -6849,7 +6890,7 @@
       <c r="AP66" s="3"/>
       <c r="AQ66" s="3"/>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -6894,7 +6935,7 @@
       <c r="AP67" s="3"/>
       <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -6939,7 +6980,7 @@
       <c r="AP68" s="3"/>
       <c r="AQ68" s="3"/>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -6984,7 +7025,7 @@
       <c r="AP69" s="3"/>
       <c r="AQ69" s="3"/>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:43">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -7029,7 +7070,7 @@
       <c r="AP70" s="3"/>
       <c r="AQ70" s="3"/>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:43">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -7074,7 +7115,7 @@
       <c r="AP71" s="3"/>
       <c r="AQ71" s="3"/>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:43">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -7119,7 +7160,7 @@
       <c r="AP72" s="3"/>
       <c r="AQ72" s="3"/>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:43">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -7164,7 +7205,7 @@
       <c r="AP73" s="3"/>
       <c r="AQ73" s="3"/>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:43">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -7209,7 +7250,7 @@
       <c r="AP74" s="3"/>
       <c r="AQ74" s="3"/>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:43">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -7254,7 +7295,7 @@
       <c r="AP75" s="3"/>
       <c r="AQ75" s="3"/>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:43">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -7299,7 +7340,7 @@
       <c r="AP76" s="3"/>
       <c r="AQ76" s="3"/>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:43">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -7344,7 +7385,7 @@
       <c r="AP77" s="3"/>
       <c r="AQ77" s="3"/>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:43">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -7389,7 +7430,7 @@
       <c r="AP78" s="3"/>
       <c r="AQ78" s="3"/>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:43">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -7434,7 +7475,7 @@
       <c r="AP79" s="3"/>
       <c r="AQ79" s="3"/>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:43">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -7479,7 +7520,7 @@
       <c r="AP80" s="3"/>
       <c r="AQ80" s="3"/>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -7524,7 +7565,7 @@
       <c r="AP81" s="3"/>
       <c r="AQ81" s="3"/>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -7569,7 +7610,7 @@
       <c r="AP82" s="3"/>
       <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -7614,7 +7655,7 @@
       <c r="AP83" s="3"/>
       <c r="AQ83" s="3"/>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -7659,7 +7700,7 @@
       <c r="AP84" s="3"/>
       <c r="AQ84" s="3"/>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -7704,7 +7745,7 @@
       <c r="AP85" s="3"/>
       <c r="AQ85" s="3"/>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -7749,7 +7790,7 @@
       <c r="AP86" s="3"/>
       <c r="AQ86" s="3"/>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:43">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -7794,7 +7835,7 @@
       <c r="AP87" s="3"/>
       <c r="AQ87" s="3"/>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -7839,7 +7880,7 @@
       <c r="AP88" s="3"/>
       <c r="AQ88" s="3"/>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -7884,7 +7925,7 @@
       <c r="AP89" s="3"/>
       <c r="AQ89" s="3"/>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -7929,7 +7970,7 @@
       <c r="AP90" s="3"/>
       <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -7969,7 +8010,7 @@
       <c r="AP91" s="3"/>
       <c r="AQ91" s="3"/>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -8009,7 +8050,7 @@
       <c r="AP92" s="3"/>
       <c r="AQ92" s="3"/>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -8049,7 +8090,7 @@
       <c r="AP93" s="3"/>
       <c r="AQ93" s="3"/>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -8074,7 +8115,7 @@
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -8099,7 +8140,7 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -8124,7 +8165,7 @@
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -8149,7 +8190,7 @@
       <c r="V97" s="3"/>
       <c r="W97" s="3"/>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -8174,7 +8215,7 @@
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -8199,7 +8240,7 @@
       <c r="V99" s="3"/>
       <c r="W99" s="3"/>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -8224,7 +8265,7 @@
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -8249,7 +8290,7 @@
       <c r="V101" s="3"/>
       <c r="W101" s="3"/>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -8274,7 +8315,7 @@
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -8299,7 +8340,7 @@
       <c r="V103" s="3"/>
       <c r="W103" s="3"/>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -8324,7 +8365,7 @@
       <c r="V104" s="3"/>
       <c r="W104" s="3"/>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -8349,7 +8390,7 @@
       <c r="V105" s="3"/>
       <c r="W105" s="3"/>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -8374,7 +8415,7 @@
       <c r="V106" s="3"/>
       <c r="W106" s="3"/>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:23">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -8399,7 +8440,7 @@
       <c r="V107" s="3"/>
       <c r="W107" s="3"/>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -8424,7 +8465,7 @@
       <c r="V108" s="3"/>
       <c r="W108" s="3"/>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:23">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -8449,7 +8490,7 @@
       <c r="V109" s="3"/>
       <c r="W109" s="3"/>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -8474,7 +8515,7 @@
       <c r="V110" s="3"/>
       <c r="W110" s="3"/>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -8499,7 +8540,7 @@
       <c r="V111" s="3"/>
       <c r="W111" s="3"/>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:23">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -8524,7 +8565,7 @@
       <c r="V112" s="3"/>
       <c r="W112" s="3"/>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -8549,7 +8590,7 @@
       <c r="V113" s="3"/>
       <c r="W113" s="3"/>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -8574,7 +8615,7 @@
       <c r="V114" s="3"/>
       <c r="W114" s="3"/>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:23">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -8599,7 +8640,7 @@
       <c r="V115" s="3"/>
       <c r="W115" s="3"/>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:23">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -8624,7 +8665,7 @@
       <c r="V116" s="3"/>
       <c r="W116" s="3"/>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:23">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -8649,7 +8690,7 @@
       <c r="V117" s="3"/>
       <c r="W117" s="3"/>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:23">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -8674,7 +8715,7 @@
       <c r="V118" s="3"/>
       <c r="W118" s="3"/>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:23">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -8699,7 +8740,7 @@
       <c r="V119" s="3"/>
       <c r="W119" s="3"/>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:23">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -8724,7 +8765,7 @@
       <c r="V120" s="3"/>
       <c r="W120" s="3"/>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -8749,7 +8790,7 @@
       <c r="V121" s="3"/>
       <c r="W121" s="3"/>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -8774,7 +8815,7 @@
       <c r="V122" s="3"/>
       <c r="W122" s="3"/>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -8799,7 +8840,7 @@
       <c r="V123" s="3"/>
       <c r="W123" s="3"/>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -8824,7 +8865,7 @@
       <c r="V124" s="3"/>
       <c r="W124" s="3"/>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:23">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -8849,7 +8890,7 @@
       <c r="V125" s="3"/>
       <c r="W125" s="3"/>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:23">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -8874,7 +8915,7 @@
       <c r="V126" s="3"/>
       <c r="W126" s="3"/>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -8899,7 +8940,7 @@
       <c r="V127" s="3"/>
       <c r="W127" s="3"/>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -8924,7 +8965,7 @@
       <c r="V128" s="3"/>
       <c r="W128" s="3"/>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:23">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -8949,7 +8990,7 @@
       <c r="V129" s="3"/>
       <c r="W129" s="3"/>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:23">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -8974,7 +9015,7 @@
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:23">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -8999,7 +9040,7 @@
       <c r="V131" s="3"/>
       <c r="W131" s="3"/>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:23">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -9024,7 +9065,7 @@
       <c r="V132" s="3"/>
       <c r="W132" s="3"/>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:23">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -9049,7 +9090,7 @@
       <c r="V133" s="3"/>
       <c r="W133" s="3"/>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:23">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -9074,7 +9115,7 @@
       <c r="V134" s="3"/>
       <c r="W134" s="3"/>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:23">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -9099,7 +9140,7 @@
       <c r="V135" s="3"/>
       <c r="W135" s="3"/>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:23">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -9124,7 +9165,7 @@
       <c r="V136" s="3"/>
       <c r="W136" s="3"/>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:23">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -9149,7 +9190,7 @@
       <c r="V137" s="3"/>
       <c r="W137" s="3"/>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:23">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -9174,7 +9215,7 @@
       <c r="V138" s="3"/>
       <c r="W138" s="3"/>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:23">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -9199,7 +9240,7 @@
       <c r="V139" s="3"/>
       <c r="W139" s="3"/>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:23">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -9224,7 +9265,7 @@
       <c r="V140" s="3"/>
       <c r="W140" s="3"/>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:23">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -9249,7 +9290,7 @@
       <c r="V141" s="3"/>
       <c r="W141" s="3"/>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:23">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -9274,7 +9315,7 @@
       <c r="V142" s="3"/>
       <c r="W142" s="3"/>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:23">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -9299,7 +9340,7 @@
       <c r="V143" s="3"/>
       <c r="W143" s="3"/>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:23">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -9324,7 +9365,7 @@
       <c r="V144" s="3"/>
       <c r="W144" s="3"/>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:23">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -9349,7 +9390,7 @@
       <c r="V145" s="3"/>
       <c r="W145" s="3"/>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:23">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -9374,7 +9415,7 @@
       <c r="V146" s="3"/>
       <c r="W146" s="3"/>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:23">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -9399,7 +9440,7 @@
       <c r="V147" s="3"/>
       <c r="W147" s="3"/>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:23">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -9424,7 +9465,7 @@
       <c r="V148" s="3"/>
       <c r="W148" s="3"/>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:23">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -9449,7 +9490,7 @@
       <c r="V149" s="3"/>
       <c r="W149" s="3"/>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:23">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -9474,7 +9515,7 @@
       <c r="V150" s="3"/>
       <c r="W150" s="3"/>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:23">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -9499,7 +9540,7 @@
       <c r="V151" s="3"/>
       <c r="W151" s="3"/>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:23">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -9524,7 +9565,7 @@
       <c r="V152" s="3"/>
       <c r="W152" s="3"/>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:23">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -9549,7 +9590,7 @@
       <c r="V153" s="3"/>
       <c r="W153" s="3"/>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:23">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -9574,7 +9615,7 @@
       <c r="V154" s="3"/>
       <c r="W154" s="3"/>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:23">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -9599,7 +9640,7 @@
       <c r="V155" s="3"/>
       <c r="W155" s="3"/>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:23">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -9624,7 +9665,7 @@
       <c r="V156" s="3"/>
       <c r="W156" s="3"/>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:23">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -9649,7 +9690,7 @@
       <c r="V157" s="3"/>
       <c r="W157" s="3"/>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:23">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -9674,7 +9715,7 @@
       <c r="V158" s="3"/>
       <c r="W158" s="3"/>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:23">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -9699,7 +9740,7 @@
       <c r="V159" s="3"/>
       <c r="W159" s="3"/>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:23">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -9724,7 +9765,7 @@
       <c r="V160" s="3"/>
       <c r="W160" s="3"/>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:23">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -9749,7 +9790,7 @@
       <c r="V161" s="3"/>
       <c r="W161" s="3"/>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -9774,7 +9815,7 @@
       <c r="V162" s="3"/>
       <c r="W162" s="3"/>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -9799,7 +9840,7 @@
       <c r="V163" s="3"/>
       <c r="W163" s="3"/>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -9824,7 +9865,7 @@
       <c r="V164" s="3"/>
       <c r="W164" s="3"/>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -9849,7 +9890,7 @@
       <c r="V165" s="3"/>
       <c r="W165" s="3"/>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -9874,7 +9915,7 @@
       <c r="V166" s="3"/>
       <c r="W166" s="3"/>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -9899,7 +9940,7 @@
       <c r="V167" s="3"/>
       <c r="W167" s="3"/>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -9924,7 +9965,7 @@
       <c r="V168" s="3"/>
       <c r="W168" s="3"/>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -9949,7 +9990,7 @@
       <c r="V169" s="3"/>
       <c r="W169" s="3"/>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -9974,7 +10015,7 @@
       <c r="V170" s="3"/>
       <c r="W170" s="3"/>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -9999,7 +10040,7 @@
       <c r="V171" s="3"/>
       <c r="W171" s="3"/>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:23">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -10024,7 +10065,7 @@
       <c r="V172" s="3"/>
       <c r="W172" s="3"/>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -10049,7 +10090,7 @@
       <c r="V173" s="3"/>
       <c r="W173" s="3"/>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -10074,7 +10115,7 @@
       <c r="V174" s="3"/>
       <c r="W174" s="3"/>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:23">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -10099,7 +10140,7 @@
       <c r="V175" s="3"/>
       <c r="W175" s="3"/>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -10124,7 +10165,7 @@
       <c r="V176" s="3"/>
       <c r="W176" s="3"/>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:23">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -10149,7 +10190,7 @@
       <c r="V177" s="3"/>
       <c r="W177" s="3"/>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:23">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -10174,7 +10215,7 @@
       <c r="V178" s="3"/>
       <c r="W178" s="3"/>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:23">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -10199,7 +10240,7 @@
       <c r="V179" s="3"/>
       <c r="W179" s="3"/>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:23">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -10224,7 +10265,7 @@
       <c r="V180" s="3"/>
       <c r="W180" s="3"/>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:23">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -10249,7 +10290,7 @@
       <c r="V181" s="3"/>
       <c r="W181" s="3"/>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:23">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -10274,7 +10315,7 @@
       <c r="V182" s="3"/>
       <c r="W182" s="3"/>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:23">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -10299,7 +10340,7 @@
       <c r="V183" s="3"/>
       <c r="W183" s="3"/>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:23">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -10324,7 +10365,7 @@
       <c r="V184" s="3"/>
       <c r="W184" s="3"/>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:23">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -10349,7 +10390,7 @@
       <c r="V185" s="3"/>
       <c r="W185" s="3"/>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:23">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -10374,7 +10415,7 @@
       <c r="V186" s="3"/>
       <c r="W186" s="3"/>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:23">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -10399,7 +10440,7 @@
       <c r="V187" s="3"/>
       <c r="W187" s="3"/>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:23">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -10424,7 +10465,7 @@
       <c r="V188" s="3"/>
       <c r="W188" s="3"/>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:23">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -10449,7 +10490,7 @@
       <c r="V189" s="3"/>
       <c r="W189" s="3"/>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:23">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -10474,7 +10515,7 @@
       <c r="V190" s="3"/>
       <c r="W190" s="3"/>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:23">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -10499,7 +10540,7 @@
       <c r="V191" s="3"/>
       <c r="W191" s="3"/>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:23">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -10524,7 +10565,7 @@
       <c r="V192" s="3"/>
       <c r="W192" s="3"/>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:23">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -10549,7 +10590,7 @@
       <c r="V193" s="3"/>
       <c r="W193" s="3"/>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:23">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -10574,7 +10615,7 @@
       <c r="V194" s="3"/>
       <c r="W194" s="3"/>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:23">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -10599,7 +10640,7 @@
       <c r="V195" s="3"/>
       <c r="W195" s="3"/>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:23">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -10624,7 +10665,7 @@
       <c r="V196" s="3"/>
       <c r="W196" s="3"/>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:23">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -10649,7 +10690,7 @@
       <c r="V197" s="3"/>
       <c r="W197" s="3"/>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:23">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -10674,7 +10715,7 @@
       <c r="V198" s="3"/>
       <c r="W198" s="3"/>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:23">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -10699,7 +10740,7 @@
       <c r="V199" s="3"/>
       <c r="W199" s="3"/>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:23">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -10724,7 +10765,7 @@
       <c r="V200" s="3"/>
       <c r="W200" s="3"/>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:23">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -10749,7 +10790,7 @@
       <c r="V201" s="3"/>
       <c r="W201" s="3"/>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:23">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -10774,7 +10815,7 @@
       <c r="V202" s="3"/>
       <c r="W202" s="3"/>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:23">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -10799,7 +10840,7 @@
       <c r="V203" s="3"/>
       <c r="W203" s="3"/>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:23">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -10824,7 +10865,7 @@
       <c r="V204" s="3"/>
       <c r="W204" s="3"/>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:23">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -10849,7 +10890,7 @@
       <c r="V205" s="3"/>
       <c r="W205" s="3"/>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:23">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -10874,7 +10915,7 @@
       <c r="V206" s="3"/>
       <c r="W206" s="3"/>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:23">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -10899,7 +10940,7 @@
       <c r="V207" s="3"/>
       <c r="W207" s="3"/>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:23">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -10924,7 +10965,7 @@
       <c r="V208" s="3"/>
       <c r="W208" s="3"/>
     </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:23">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -10949,7 +10990,7 @@
       <c r="V209" s="3"/>
       <c r="W209" s="3"/>
     </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:23">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -10974,7 +11015,7 @@
       <c r="V210" s="3"/>
       <c r="W210" s="3"/>
     </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:23">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -10999,7 +11040,7 @@
       <c r="V211" s="3"/>
       <c r="W211" s="3"/>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:23">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -11024,7 +11065,7 @@
       <c r="V212" s="3"/>
       <c r="W212" s="3"/>
     </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:23">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -11049,7 +11090,7 @@
       <c r="V213" s="3"/>
       <c r="W213" s="3"/>
     </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:23">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -11074,7 +11115,7 @@
       <c r="V214" s="3"/>
       <c r="W214" s="3"/>
     </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:23">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -11099,7 +11140,7 @@
       <c r="V215" s="3"/>
       <c r="W215" s="3"/>
     </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:23">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -11124,7 +11165,7 @@
       <c r="V216" s="3"/>
       <c r="W216" s="3"/>
     </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -11149,7 +11190,7 @@
       <c r="V217" s="3"/>
       <c r="W217" s="3"/>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -11174,7 +11215,7 @@
       <c r="V218" s="3"/>
       <c r="W218" s="3"/>
     </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:23">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -11199,7 +11240,7 @@
       <c r="V219" s="3"/>
       <c r="W219" s="3"/>
     </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -11224,7 +11265,7 @@
       <c r="V220" s="3"/>
       <c r="W220" s="3"/>
     </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -11249,7 +11290,7 @@
       <c r="V221" s="3"/>
       <c r="W221" s="3"/>
     </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -11274,7 +11315,7 @@
       <c r="V222" s="3"/>
       <c r="W222" s="3"/>
     </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:23">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -11299,7 +11340,7 @@
       <c r="V223" s="3"/>
       <c r="W223" s="3"/>
     </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:23">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -11324,7 +11365,7 @@
       <c r="V224" s="3"/>
       <c r="W224" s="3"/>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:23">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -11349,7 +11390,7 @@
       <c r="V225" s="3"/>
       <c r="W225" s="3"/>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:23">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -11374,7 +11415,7 @@
       <c r="V226" s="3"/>
       <c r="W226" s="3"/>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -11399,7 +11440,7 @@
       <c r="V227" s="3"/>
       <c r="W227" s="3"/>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -11424,7 +11465,7 @@
       <c r="V228" s="3"/>
       <c r="W228" s="3"/>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -11449,7 +11490,7 @@
       <c r="V229" s="3"/>
       <c r="W229" s="3"/>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -11474,7 +11515,7 @@
       <c r="V230" s="3"/>
       <c r="W230" s="3"/>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:23">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -11499,7 +11540,7 @@
       <c r="V231" s="3"/>
       <c r="W231" s="3"/>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:23">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -11524,7 +11565,7 @@
       <c r="V232" s="3"/>
       <c r="W232" s="3"/>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:23">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -11549,7 +11590,7 @@
       <c r="V233" s="3"/>
       <c r="W233" s="3"/>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -11574,7 +11615,7 @@
       <c r="V234" s="3"/>
       <c r="W234" s="3"/>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:23">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -11599,7 +11640,7 @@
       <c r="V235" s="3"/>
       <c r="W235" s="3"/>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:23">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -11624,7 +11665,7 @@
       <c r="V236" s="3"/>
       <c r="W236" s="3"/>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:23">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -11649,7 +11690,7 @@
       <c r="V237" s="3"/>
       <c r="W237" s="3"/>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -11674,7 +11715,7 @@
       <c r="V238" s="3"/>
       <c r="W238" s="3"/>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:23">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -11699,7 +11740,7 @@
       <c r="V239" s="3"/>
       <c r="W239" s="3"/>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:23">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -11724,7 +11765,7 @@
       <c r="V240" s="3"/>
       <c r="W240" s="3"/>
     </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -11749,7 +11790,7 @@
       <c r="V241" s="3"/>
       <c r="W241" s="3"/>
     </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -11774,7 +11815,7 @@
       <c r="V242" s="3"/>
       <c r="W242" s="3"/>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -11799,7 +11840,7 @@
       <c r="V243" s="3"/>
       <c r="W243" s="3"/>
     </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:23">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -11824,7 +11865,7 @@
       <c r="V244" s="3"/>
       <c r="W244" s="3"/>
     </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:23">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -11849,7 +11890,7 @@
       <c r="V245" s="3"/>
       <c r="W245" s="3"/>
     </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:23">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -11874,7 +11915,7 @@
       <c r="V246" s="3"/>
       <c r="W246" s="3"/>
     </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:23">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -11899,7 +11940,7 @@
       <c r="V247" s="3"/>
       <c r="W247" s="3"/>
     </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:23">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -11924,7 +11965,7 @@
       <c r="V248" s="3"/>
       <c r="W248" s="3"/>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -11949,7 +11990,7 @@
       <c r="V249" s="3"/>
       <c r="W249" s="3"/>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:23">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -11974,7 +12015,7 @@
       <c r="V250" s="3"/>
       <c r="W250" s="3"/>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:23">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -11999,7 +12040,7 @@
       <c r="V251" s="3"/>
       <c r="W251" s="3"/>
     </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -12024,7 +12065,7 @@
       <c r="V252" s="3"/>
       <c r="W252" s="3"/>
     </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:23">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -12049,7 +12090,7 @@
       <c r="V253" s="3"/>
       <c r="W253" s="3"/>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:23">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -12074,7 +12115,7 @@
       <c r="V254" s="3"/>
       <c r="W254" s="3"/>
     </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:23">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -12099,7 +12140,7 @@
       <c r="V255" s="3"/>
       <c r="W255" s="3"/>
     </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:23">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -12124,7 +12165,7 @@
       <c r="V256" s="3"/>
       <c r="W256" s="3"/>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:23">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -12149,7 +12190,7 @@
       <c r="V257" s="3"/>
       <c r="W257" s="3"/>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:23">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -12174,7 +12215,7 @@
       <c r="V258" s="3"/>
       <c r="W258" s="3"/>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:23">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -12199,7 +12240,7 @@
       <c r="V259" s="3"/>
       <c r="W259" s="3"/>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:23">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -12224,7 +12265,7 @@
       <c r="V260" s="3"/>
       <c r="W260" s="3"/>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:23">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -12249,7 +12290,7 @@
       <c r="V261" s="3"/>
       <c r="W261" s="3"/>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:23">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -12274,7 +12315,7 @@
       <c r="V262" s="3"/>
       <c r="W262" s="3"/>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:23">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -12299,7 +12340,7 @@
       <c r="V263" s="3"/>
       <c r="W263" s="3"/>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -12324,7 +12365,7 @@
       <c r="V264" s="3"/>
       <c r="W264" s="3"/>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:23">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -12349,7 +12390,7 @@
       <c r="V265" s="3"/>
       <c r="W265" s="3"/>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:23">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -12374,7 +12415,7 @@
       <c r="V266" s="3"/>
       <c r="W266" s="3"/>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:23">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -12399,7 +12440,7 @@
       <c r="V267" s="3"/>
       <c r="W267" s="3"/>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:23">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -12424,7 +12465,7 @@
       <c r="V268" s="3"/>
       <c r="W268" s="3"/>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -12449,7 +12490,7 @@
       <c r="V269" s="3"/>
       <c r="W269" s="3"/>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:23">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -12474,7 +12515,7 @@
       <c r="V270" s="3"/>
       <c r="W270" s="3"/>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -12499,7 +12540,7 @@
       <c r="V271" s="3"/>
       <c r="W271" s="3"/>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -12524,7 +12565,7 @@
       <c r="V272" s="3"/>
       <c r="W272" s="3"/>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -12549,7 +12590,7 @@
       <c r="V273" s="3"/>
       <c r="W273" s="3"/>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:23">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -12574,7 +12615,7 @@
       <c r="V274" s="3"/>
       <c r="W274" s="3"/>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:23">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -12599,7 +12640,7 @@
       <c r="V275" s="3"/>
       <c r="W275" s="3"/>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:23">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -12624,7 +12665,7 @@
       <c r="V276" s="3"/>
       <c r="W276" s="3"/>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:23">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -12649,7 +12690,7 @@
       <c r="V277" s="3"/>
       <c r="W277" s="3"/>
     </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:23">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -12674,7 +12715,7 @@
       <c r="V278" s="3"/>
       <c r="W278" s="3"/>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:23">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -12699,7 +12740,7 @@
       <c r="V279" s="3"/>
       <c r="W279" s="3"/>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:23">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -12724,7 +12765,7 @@
       <c r="V280" s="3"/>
       <c r="W280" s="3"/>
     </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:23">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -12749,7 +12790,7 @@
       <c r="V281" s="3"/>
       <c r="W281" s="3"/>
     </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:23">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -12774,7 +12815,7 @@
       <c r="V282" s="3"/>
       <c r="W282" s="3"/>
     </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:23">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -12799,7 +12840,7 @@
       <c r="V283" s="3"/>
       <c r="W283" s="3"/>
     </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:23">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -12824,7 +12865,7 @@
       <c r="V284" s="3"/>
       <c r="W284" s="3"/>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:23">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -12849,7 +12890,7 @@
       <c r="V285" s="3"/>
       <c r="W285" s="3"/>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:23">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -12874,7 +12915,7 @@
       <c r="V286" s="3"/>
       <c r="W286" s="3"/>
     </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:23">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -12899,7 +12940,7 @@
       <c r="V287" s="3"/>
       <c r="W287" s="3"/>
     </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -12924,7 +12965,7 @@
       <c r="V288" s="3"/>
       <c r="W288" s="3"/>
     </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:23">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -12949,7 +12990,7 @@
       <c r="V289" s="3"/>
       <c r="W289" s="3"/>
     </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:23">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -12974,7 +13015,7 @@
       <c r="V290" s="3"/>
       <c r="W290" s="3"/>
     </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:23">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -12999,7 +13040,7 @@
       <c r="V291" s="3"/>
       <c r="W291" s="3"/>
     </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:23">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -13024,7 +13065,7 @@
       <c r="V292" s="3"/>
       <c r="W292" s="3"/>
     </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:23">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -13049,7 +13090,7 @@
       <c r="V293" s="3"/>
       <c r="W293" s="3"/>
     </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:23">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -13074,7 +13115,7 @@
       <c r="V294" s="3"/>
       <c r="W294" s="3"/>
     </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:23">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -13099,7 +13140,7 @@
       <c r="V295" s="3"/>
       <c r="W295" s="3"/>
     </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:23">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -13124,7 +13165,7 @@
       <c r="V296" s="3"/>
       <c r="W296" s="3"/>
     </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:23">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -13149,7 +13190,7 @@
       <c r="V297" s="3"/>
       <c r="W297" s="3"/>
     </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:23">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -13174,7 +13215,7 @@
       <c r="V298" s="3"/>
       <c r="W298" s="3"/>
     </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:23">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -13199,7 +13240,7 @@
       <c r="V299" s="3"/>
       <c r="W299" s="3"/>
     </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:23">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -13224,7 +13265,7 @@
       <c r="V300" s="3"/>
       <c r="W300" s="3"/>
     </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:23">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -13249,7 +13290,7 @@
       <c r="V301" s="3"/>
       <c r="W301" s="3"/>
     </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:23">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -13274,7 +13315,7 @@
       <c r="V302" s="3"/>
       <c r="W302" s="3"/>
     </row>
-    <row r="303" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:23">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -13299,7 +13340,7 @@
       <c r="V303" s="3"/>
       <c r="W303" s="3"/>
     </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:23">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -13324,7 +13365,7 @@
       <c r="V304" s="3"/>
       <c r="W304" s="3"/>
     </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:23">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -13349,7 +13390,7 @@
       <c r="V305" s="3"/>
       <c r="W305" s="3"/>
     </row>
-    <row r="306" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:23">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -13374,7 +13415,7 @@
       <c r="V306" s="3"/>
       <c r="W306" s="3"/>
     </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:23">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -13399,7 +13440,7 @@
       <c r="V307" s="3"/>
       <c r="W307" s="3"/>
     </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:23">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -13424,7 +13465,7 @@
       <c r="V308" s="3"/>
       <c r="W308" s="3"/>
     </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:23">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -13449,7 +13490,7 @@
       <c r="V309" s="3"/>
       <c r="W309" s="3"/>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:23">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -13474,7 +13515,7 @@
       <c r="V310" s="3"/>
       <c r="W310" s="3"/>
     </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:23">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -13499,7 +13540,7 @@
       <c r="V311" s="3"/>
       <c r="W311" s="3"/>
     </row>
-    <row r="312" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:23">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -13524,7 +13565,7 @@
       <c r="V312" s="3"/>
       <c r="W312" s="3"/>
     </row>
-    <row r="313" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:23">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -13549,7 +13590,7 @@
       <c r="V313" s="3"/>
       <c r="W313" s="3"/>
     </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:23">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -13574,7 +13615,7 @@
       <c r="V314" s="3"/>
       <c r="W314" s="3"/>
     </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:23">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -13599,7 +13640,7 @@
       <c r="V315" s="3"/>
       <c r="W315" s="3"/>
     </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:23">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -13624,7 +13665,7 @@
       <c r="V316" s="3"/>
       <c r="W316" s="3"/>
     </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:23">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -13649,7 +13690,7 @@
       <c r="V317" s="3"/>
       <c r="W317" s="3"/>
     </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:23">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -13674,7 +13715,7 @@
       <c r="V318" s="3"/>
       <c r="W318" s="3"/>
     </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:23">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -13699,7 +13740,7 @@
       <c r="V319" s="3"/>
       <c r="W319" s="3"/>
     </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:23">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -13724,7 +13765,7 @@
       <c r="V320" s="3"/>
       <c r="W320" s="3"/>
     </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:23">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -13749,7 +13790,7 @@
       <c r="V321" s="3"/>
       <c r="W321" s="3"/>
     </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:23">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -13774,7 +13815,7 @@
       <c r="V322" s="3"/>
       <c r="W322" s="3"/>
     </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:23">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -13799,7 +13840,7 @@
       <c r="V323" s="3"/>
       <c r="W323" s="3"/>
     </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:23">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -13824,7 +13865,7 @@
       <c r="V324" s="3"/>
       <c r="W324" s="3"/>
     </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:23">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -13849,7 +13890,7 @@
       <c r="V325" s="3"/>
       <c r="W325" s="3"/>
     </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:23">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -13874,7 +13915,7 @@
       <c r="V326" s="3"/>
       <c r="W326" s="3"/>
     </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:23">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -13899,7 +13940,7 @@
       <c r="V327" s="3"/>
       <c r="W327" s="3"/>
     </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:23">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -13924,7 +13965,7 @@
       <c r="V328" s="3"/>
       <c r="W328" s="3"/>
     </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:23">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -13949,7 +13990,7 @@
       <c r="V329" s="3"/>
       <c r="W329" s="3"/>
     </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:23">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -13974,7 +14015,7 @@
       <c r="V330" s="3"/>
       <c r="W330" s="3"/>
     </row>
-    <row r="331" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:23">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -13999,7 +14040,7 @@
       <c r="V331" s="3"/>
       <c r="W331" s="3"/>
     </row>
-    <row r="332" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:23">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -14024,7 +14065,7 @@
       <c r="V332" s="3"/>
       <c r="W332" s="3"/>
     </row>
-    <row r="333" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:23">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -14049,7 +14090,7 @@
       <c r="V333" s="3"/>
       <c r="W333" s="3"/>
     </row>
-    <row r="334" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:23">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -14074,7 +14115,7 @@
       <c r="V334" s="3"/>
       <c r="W334" s="3"/>
     </row>
-    <row r="335" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:23">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -14099,7 +14140,7 @@
       <c r="V335" s="3"/>
       <c r="W335" s="3"/>
     </row>
-    <row r="336" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:23">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -14124,7 +14165,7 @@
       <c r="V336" s="3"/>
       <c r="W336" s="3"/>
     </row>
-    <row r="337" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:23">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -14149,7 +14190,7 @@
       <c r="V337" s="3"/>
       <c r="W337" s="3"/>
     </row>
-    <row r="338" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:23">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -14174,7 +14215,7 @@
       <c r="V338" s="3"/>
       <c r="W338" s="3"/>
     </row>
-    <row r="339" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:23">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -14199,7 +14240,7 @@
       <c r="V339" s="3"/>
       <c r="W339" s="3"/>
     </row>
-    <row r="340" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:23">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -14224,7 +14265,7 @@
       <c r="V340" s="3"/>
       <c r="W340" s="3"/>
     </row>
-    <row r="341" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:23">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -14249,7 +14290,7 @@
       <c r="V341" s="3"/>
       <c r="W341" s="3"/>
     </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:23">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -14274,7 +14315,7 @@
       <c r="V342" s="3"/>
       <c r="W342" s="3"/>
     </row>
-    <row r="343" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:23">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -14299,7 +14340,7 @@
       <c r="V343" s="3"/>
       <c r="W343" s="3"/>
     </row>
-    <row r="344" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:23">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -14324,7 +14365,7 @@
       <c r="V344" s="3"/>
       <c r="W344" s="3"/>
     </row>
-    <row r="345" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:23">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -14349,7 +14390,7 @@
       <c r="V345" s="3"/>
       <c r="W345" s="3"/>
     </row>
-    <row r="346" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:23">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -14374,7 +14415,7 @@
       <c r="V346" s="3"/>
       <c r="W346" s="3"/>
     </row>
-    <row r="347" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:23">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -14399,7 +14440,7 @@
       <c r="V347" s="3"/>
       <c r="W347" s="3"/>
     </row>
-    <row r="348" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:23">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -14424,7 +14465,7 @@
       <c r="V348" s="3"/>
       <c r="W348" s="3"/>
     </row>
-    <row r="349" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:23">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -14449,7 +14490,7 @@
       <c r="V349" s="3"/>
       <c r="W349" s="3"/>
     </row>
-    <row r="350" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:23">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -14474,7 +14515,7 @@
       <c r="V350" s="3"/>
       <c r="W350" s="3"/>
     </row>
-    <row r="351" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:23">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -14499,7 +14540,7 @@
       <c r="V351" s="3"/>
       <c r="W351" s="3"/>
     </row>
-    <row r="352" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:23">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -14524,7 +14565,7 @@
       <c r="V352" s="3"/>
       <c r="W352" s="3"/>
     </row>
-    <row r="353" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:23">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -14549,7 +14590,7 @@
       <c r="V353" s="3"/>
       <c r="W353" s="3"/>
     </row>
-    <row r="354" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:23">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -14574,7 +14615,7 @@
       <c r="V354" s="3"/>
       <c r="W354" s="3"/>
     </row>
-    <row r="355" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:23">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -14599,7 +14640,7 @@
       <c r="V355" s="3"/>
       <c r="W355" s="3"/>
     </row>
-    <row r="356" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:23">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -14624,7 +14665,7 @@
       <c r="V356" s="3"/>
       <c r="W356" s="3"/>
     </row>
-    <row r="357" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:23">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -14649,7 +14690,7 @@
       <c r="V357" s="3"/>
       <c r="W357" s="3"/>
     </row>
-    <row r="358" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:23">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -14674,7 +14715,7 @@
       <c r="V358" s="3"/>
       <c r="W358" s="3"/>
     </row>
-    <row r="359" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:23">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -14699,7 +14740,7 @@
       <c r="V359" s="3"/>
       <c r="W359" s="3"/>
     </row>
-    <row r="360" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:23">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -14724,7 +14765,7 @@
       <c r="V360" s="3"/>
       <c r="W360" s="3"/>
     </row>
-    <row r="361" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:23">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -14749,7 +14790,7 @@
       <c r="V361" s="3"/>
       <c r="W361" s="3"/>
     </row>
-    <row r="362" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:23">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -14774,7 +14815,7 @@
       <c r="V362" s="3"/>
       <c r="W362" s="3"/>
     </row>
-    <row r="363" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:23">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -14799,7 +14840,7 @@
       <c r="V363" s="3"/>
       <c r="W363" s="3"/>
     </row>
-    <row r="364" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:23">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -14824,7 +14865,7 @@
       <c r="V364" s="3"/>
       <c r="W364" s="3"/>
     </row>
-    <row r="365" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:23">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -14849,7 +14890,7 @@
       <c r="V365" s="3"/>
       <c r="W365" s="3"/>
     </row>
-    <row r="366" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:23">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -14874,7 +14915,7 @@
       <c r="V366" s="3"/>
       <c r="W366" s="3"/>
     </row>
-    <row r="367" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:23">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -14899,7 +14940,7 @@
       <c r="V367" s="3"/>
       <c r="W367" s="3"/>
     </row>
-    <row r="368" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:23">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -14924,7 +14965,7 @@
       <c r="V368" s="3"/>
       <c r="W368" s="3"/>
     </row>
-    <row r="369" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:23">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -14949,7 +14990,7 @@
       <c r="V369" s="3"/>
       <c r="W369" s="3"/>
     </row>
-    <row r="370" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:23">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -14974,7 +15015,7 @@
       <c r="V370" s="3"/>
       <c r="W370" s="3"/>
     </row>
-    <row r="371" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:23">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -14999,7 +15040,7 @@
       <c r="V371" s="3"/>
       <c r="W371" s="3"/>
     </row>
-    <row r="372" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:23">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -15024,7 +15065,7 @@
       <c r="V372" s="3"/>
       <c r="W372" s="3"/>
     </row>
-    <row r="373" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:23">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -15049,7 +15090,7 @@
       <c r="V373" s="3"/>
       <c r="W373" s="3"/>
     </row>
-    <row r="374" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:23">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -15074,7 +15115,7 @@
       <c r="V374" s="3"/>
       <c r="W374" s="3"/>
     </row>
-    <row r="375" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:23">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -15099,7 +15140,7 @@
       <c r="V375" s="3"/>
       <c r="W375" s="3"/>
     </row>
-    <row r="376" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:23">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -15124,7 +15165,7 @@
       <c r="V376" s="3"/>
       <c r="W376" s="3"/>
     </row>
-    <row r="377" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:23">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -15149,7 +15190,7 @@
       <c r="V377" s="3"/>
       <c r="W377" s="3"/>
     </row>
-    <row r="378" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:23">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -15174,7 +15215,7 @@
       <c r="V378" s="3"/>
       <c r="W378" s="3"/>
     </row>
-    <row r="379" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:23">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -15199,7 +15240,7 @@
       <c r="V379" s="3"/>
       <c r="W379" s="3"/>
     </row>
-    <row r="380" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:23">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -15224,7 +15265,7 @@
       <c r="V380" s="3"/>
       <c r="W380" s="3"/>
     </row>
-    <row r="381" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:23">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -15249,7 +15290,7 @@
       <c r="V381" s="3"/>
       <c r="W381" s="3"/>
     </row>
-    <row r="382" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:23">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -15274,7 +15315,7 @@
       <c r="V382" s="3"/>
       <c r="W382" s="3"/>
     </row>
-    <row r="383" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:23">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -15299,7 +15340,7 @@
       <c r="V383" s="3"/>
       <c r="W383" s="3"/>
     </row>
-    <row r="384" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:23">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -15324,7 +15365,7 @@
       <c r="V384" s="3"/>
       <c r="W384" s="3"/>
     </row>
-    <row r="385" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:23">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -15349,7 +15390,7 @@
       <c r="V385" s="3"/>
       <c r="W385" s="3"/>
     </row>
-    <row r="386" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:23">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -15374,7 +15415,7 @@
       <c r="V386" s="3"/>
       <c r="W386" s="3"/>
     </row>
-    <row r="387" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:23">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -15399,7 +15440,7 @@
       <c r="V387" s="3"/>
       <c r="W387" s="3"/>
     </row>
-    <row r="388" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:23">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -15424,7 +15465,7 @@
       <c r="V388" s="3"/>
       <c r="W388" s="3"/>
     </row>
-    <row r="389" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:23">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -15449,7 +15490,7 @@
       <c r="V389" s="3"/>
       <c r="W389" s="3"/>
     </row>
-    <row r="390" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:23">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -15474,7 +15515,7 @@
       <c r="V390" s="3"/>
       <c r="W390" s="3"/>
     </row>
-    <row r="391" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:23">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -15499,7 +15540,7 @@
       <c r="V391" s="3"/>
       <c r="W391" s="3"/>
     </row>
-    <row r="392" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:23">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -15524,7 +15565,7 @@
       <c r="V392" s="3"/>
       <c r="W392" s="3"/>
     </row>
-    <row r="393" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:23">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -15549,7 +15590,7 @@
       <c r="V393" s="3"/>
       <c r="W393" s="3"/>
     </row>
-    <row r="394" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:23">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -15574,7 +15615,7 @@
       <c r="V394" s="3"/>
       <c r="W394" s="3"/>
     </row>
-    <row r="395" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:23">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -15599,7 +15640,7 @@
       <c r="V395" s="3"/>
       <c r="W395" s="3"/>
     </row>
-    <row r="396" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:23">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -15624,7 +15665,7 @@
       <c r="V396" s="3"/>
       <c r="W396" s="3"/>
     </row>
-    <row r="397" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:23">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -15649,7 +15690,7 @@
       <c r="V397" s="3"/>
       <c r="W397" s="3"/>
     </row>
-    <row r="398" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:23">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -15674,7 +15715,7 @@
       <c r="V398" s="3"/>
       <c r="W398" s="3"/>
     </row>
-    <row r="399" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:23">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -15699,7 +15740,7 @@
       <c r="V399" s="3"/>
       <c r="W399" s="3"/>
     </row>
-    <row r="400" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:23">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -15724,7 +15765,7 @@
       <c r="V400" s="3"/>
       <c r="W400" s="3"/>
     </row>
-    <row r="401" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:23">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -15749,7 +15790,7 @@
       <c r="V401" s="3"/>
       <c r="W401" s="3"/>
     </row>
-    <row r="402" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:23">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -15774,7 +15815,7 @@
       <c r="V402" s="3"/>
       <c r="W402" s="3"/>
     </row>
-    <row r="403" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:23">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -15799,7 +15840,7 @@
       <c r="V403" s="3"/>
       <c r="W403" s="3"/>
     </row>
-    <row r="404" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:23">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -15824,7 +15865,7 @@
       <c r="V404" s="3"/>
       <c r="W404" s="3"/>
     </row>
-    <row r="405" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:23">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -15849,7 +15890,7 @@
       <c r="V405" s="3"/>
       <c r="W405" s="3"/>
     </row>
-    <row r="406" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:23">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -15874,7 +15915,7 @@
       <c r="V406" s="3"/>
       <c r="W406" s="3"/>
     </row>
-    <row r="407" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:23">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -15899,7 +15940,7 @@
       <c r="V407" s="3"/>
       <c r="W407" s="3"/>
     </row>
-    <row r="408" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:23">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -15924,7 +15965,7 @@
       <c r="V408" s="3"/>
       <c r="W408" s="3"/>
     </row>
-    <row r="409" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:23">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -15949,7 +15990,7 @@
       <c r="V409" s="3"/>
       <c r="W409" s="3"/>
     </row>
-    <row r="410" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:23">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -15974,7 +16015,7 @@
       <c r="V410" s="3"/>
       <c r="W410" s="3"/>
     </row>
-    <row r="411" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:23">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -15999,7 +16040,7 @@
       <c r="V411" s="3"/>
       <c r="W411" s="3"/>
     </row>
-    <row r="412" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:23">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -16024,7 +16065,7 @@
       <c r="V412" s="3"/>
       <c r="W412" s="3"/>
     </row>
-    <row r="413" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:23">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -16049,7 +16090,7 @@
       <c r="V413" s="3"/>
       <c r="W413" s="3"/>
     </row>
-    <row r="414" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:23">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -16074,7 +16115,7 @@
       <c r="V414" s="3"/>
       <c r="W414" s="3"/>
     </row>
-    <row r="415" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:23">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -16099,7 +16140,7 @@
       <c r="V415" s="3"/>
       <c r="W415" s="3"/>
     </row>
-    <row r="416" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:23">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -16124,7 +16165,7 @@
       <c r="V416" s="3"/>
       <c r="W416" s="3"/>
     </row>
-    <row r="417" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:23">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -16149,7 +16190,7 @@
       <c r="V417" s="3"/>
       <c r="W417" s="3"/>
     </row>
-    <row r="418" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:23">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -16174,7 +16215,7 @@
       <c r="V418" s="3"/>
       <c r="W418" s="3"/>
     </row>
-    <row r="419" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:23">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -16199,7 +16240,7 @@
       <c r="V419" s="3"/>
       <c r="W419" s="3"/>
     </row>
-    <row r="420" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:23">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -16224,7 +16265,7 @@
       <c r="V420" s="3"/>
       <c r="W420" s="3"/>
     </row>
-    <row r="421" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:23">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -16249,7 +16290,7 @@
       <c r="V421" s="3"/>
       <c r="W421" s="3"/>
     </row>
-    <row r="422" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:23">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -16274,7 +16315,7 @@
       <c r="V422" s="3"/>
       <c r="W422" s="3"/>
     </row>
-    <row r="423" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:23">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -16299,7 +16340,7 @@
       <c r="V423" s="3"/>
       <c r="W423" s="3"/>
     </row>
-    <row r="424" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:23">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -16324,7 +16365,7 @@
       <c r="V424" s="3"/>
       <c r="W424" s="3"/>
     </row>
-    <row r="425" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:23">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -16349,7 +16390,7 @@
       <c r="V425" s="3"/>
       <c r="W425" s="3"/>
     </row>
-    <row r="426" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:23">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -16374,7 +16415,7 @@
       <c r="V426" s="3"/>
       <c r="W426" s="3"/>
     </row>
-    <row r="427" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:23">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -16399,7 +16440,7 @@
       <c r="V427" s="3"/>
       <c r="W427" s="3"/>
     </row>
-    <row r="428" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:23">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -16424,7 +16465,7 @@
       <c r="V428" s="3"/>
       <c r="W428" s="3"/>
     </row>
-    <row r="429" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:23">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -16449,7 +16490,7 @@
       <c r="V429" s="3"/>
       <c r="W429" s="3"/>
     </row>
-    <row r="430" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:23">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -16474,7 +16515,7 @@
       <c r="V430" s="3"/>
       <c r="W430" s="3"/>
     </row>
-    <row r="431" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:23">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -16499,7 +16540,7 @@
       <c r="V431" s="3"/>
       <c r="W431" s="3"/>
     </row>
-    <row r="432" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:23">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -16524,7 +16565,7 @@
       <c r="V432" s="3"/>
       <c r="W432" s="3"/>
     </row>
-    <row r="433" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:23">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -16549,7 +16590,7 @@
       <c r="V433" s="3"/>
       <c r="W433" s="3"/>
     </row>
-    <row r="434" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:23">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -16573,7 +16614,7 @@
       <c r="U434" s="3"/>
       <c r="V434" s="3"/>
     </row>
-    <row r="435" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:23">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -16597,7 +16638,7 @@
       <c r="U435" s="3"/>
       <c r="V435" s="3"/>
     </row>
-    <row r="436" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:23">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -16718,55 +16759,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E503ABFF-7BF5-4558-9326-F1049C4EC842}">
   <dimension ref="B1:V37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.08203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="4.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.08203125" customWidth="1"/>
+    <col min="3" max="3" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="4.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="79.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.58203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="79.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.875" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="14.25" customWidth="1"/>
-    <col min="16" max="16" width="15.83203125" customWidth="1"/>
-    <col min="19" max="19" width="35.33203125" customWidth="1"/>
+    <col min="16" max="16" width="15.875" customWidth="1"/>
+    <col min="19" max="19" width="35.375" customWidth="1"/>
     <col min="20" max="21" width="28" customWidth="1"/>
     <col min="22" max="22" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="132" t="s">
+    <row r="1" spans="2:22" ht="40.15" customHeight="1" thickBot="1">
+      <c r="B1" s="131" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="F1" s="132" t="s">
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="F1" s="131" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="L1" s="133" t="s">
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="L1" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="R1" s="133" t="s">
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="R1" s="132" t="s">
         <v>49</v>
       </c>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-    </row>
-    <row r="2" spans="2:22" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="133"/>
+    </row>
+    <row r="2" spans="2:22" ht="16.149999999999999" thickBot="1">
       <c r="B2" s="91" t="s">
         <v>143</v>
       </c>
@@ -16823,7 +16864,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:22">
       <c r="B3" s="89" t="s">
         <v>153</v>
       </c>
@@ -16881,7 +16922,7 @@
         <v>3500000</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:22">
       <c r="B4" s="88" t="s">
         <v>162</v>
       </c>
@@ -16940,7 +16981,7 @@
         <v>8500000</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:22">
       <c r="B5" s="88" t="s">
         <v>170</v>
       </c>
@@ -16998,7 +17039,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:22">
       <c r="B6" s="88" t="s">
         <v>177</v>
       </c>
@@ -17056,7 +17097,7 @@
         <v>3400000</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:22">
       <c r="B7" s="88" t="s">
         <v>183</v>
       </c>
@@ -17098,18 +17139,18 @@
       <c r="P7" s="104">
         <v>120000</v>
       </c>
-      <c r="R7" s="135" t="s">
+      <c r="R7" s="134" t="s">
         <v>185</v>
       </c>
-      <c r="S7" s="136"/>
-      <c r="T7" s="136"/>
-      <c r="U7" s="137"/>
+      <c r="S7" s="135"/>
+      <c r="T7" s="135"/>
+      <c r="U7" s="136"/>
       <c r="V7" s="105">
         <f>SUM(V3:V6)</f>
         <v>16900000</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:22">
       <c r="B8" s="109" t="s">
         <v>186</v>
       </c>
@@ -17151,7 +17192,7 @@
         <v>1080000</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:22">
       <c r="B9" s="88" t="s">
         <v>185</v>
       </c>
@@ -17179,18 +17220,18 @@
         <f>I9/C12</f>
         <v>3105.1552795031057</v>
       </c>
-      <c r="L9" s="135" t="s">
+      <c r="L9" s="134" t="s">
         <v>191</v>
       </c>
-      <c r="M9" s="135"/>
-      <c r="N9" s="135"/>
+      <c r="M9" s="134"/>
+      <c r="N9" s="134"/>
       <c r="O9" s="103"/>
       <c r="P9" s="105">
         <f>SUM(P3:P8)</f>
         <v>1540000</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:22">
       <c r="F10" s="94" t="s">
         <v>192</v>
       </c>
@@ -17208,7 +17249,7 @@
         <v>3105.1552795031057</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:22">
       <c r="F11" s="94" t="s">
         <v>193</v>
       </c>
@@ -17226,7 +17267,7 @@
         <v>3105.1552795031057</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:22">
       <c r="B12" s="110" t="s">
         <v>194</v>
       </c>
@@ -17250,7 +17291,7 @@
         <v>2981.3664596273293</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:22">
       <c r="F13" s="94" t="s">
         <v>198</v>
       </c>
@@ -17268,7 +17309,7 @@
         <v>2236.0248447204967</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:22">
       <c r="F14" s="94" t="s">
         <v>200</v>
       </c>
@@ -17286,7 +17327,7 @@
         <v>11180.124223602485</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:22">
       <c r="F15" s="94" t="s">
         <v>202</v>
       </c>
@@ -17304,7 +17345,7 @@
         <v>11180.124223602485</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:22">
       <c r="F16" s="94" t="s">
         <v>204</v>
       </c>
@@ -17322,12 +17363,12 @@
         <v>8944.0993788819869</v>
       </c>
     </row>
-    <row r="17" spans="6:10" x14ac:dyDescent="0.35">
-      <c r="F17" s="135" t="s">
+    <row r="17" spans="6:10">
+      <c r="F17" s="134" t="s">
         <v>185</v>
       </c>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="134"/>
       <c r="I17" s="105">
         <f>SUM(I3:I16)</f>
         <v>24698390</v>
@@ -17337,13 +17378,13 @@
         <v>153406.14906832299</v>
       </c>
     </row>
-    <row r="35" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="8:8">
       <c r="H35" s="106"/>
     </row>
-    <row r="36" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="8:8">
       <c r="H36" s="106"/>
     </row>
-    <row r="37" spans="8:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="8:8">
       <c r="H37" s="106"/>
     </row>
   </sheetData>
@@ -17367,17 +17408,17 @@
     <tabColor theme="0" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="9"/>
-    <col min="3" max="3" width="3.33203125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="3.33203125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="3.33203125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="9"/>
+    <col min="3" max="3" width="3.375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="3.375" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="3.375" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="9" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:32" s="9" customFormat="1" ht="42" customHeight="1" thickBot="1">
       <c r="B1" s="33" t="s">
         <v>206</v>
       </c>
@@ -17405,7 +17446,7 @@
       <c r="AE1" s="8"/>
       <c r="AF1" s="8"/>
     </row>
-    <row r="2" spans="1:32" ht="25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" ht="24.95" customHeight="1" thickTop="1">
       <c r="A2" s="8"/>
       <c r="B2" s="32" t="s">
         <v>207</v>
@@ -17420,7 +17461,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" ht="35.1" customHeight="1">
       <c r="A3" s="8"/>
       <c r="B3" s="31" t="s">
         <v>209</v>
@@ -17435,7 +17476,7 @@
       </c>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" ht="35.1" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="29" t="s">
         <v>211</v>
@@ -17446,15 +17487,15 @@
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="71" t="s">
-        <v>96</v>
+        <v>213</v>
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" ht="35.1" customHeight="1">
       <c r="A5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="27" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="72" t="s">
@@ -17462,46 +17503,46 @@
       </c>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" ht="35.1" customHeight="1">
       <c r="A6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="23"/>
       <c r="E6" s="8"/>
       <c r="F6" s="26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" ht="35.1" customHeight="1">
       <c r="A7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="23"/>
       <c r="E7" s="8"/>
       <c r="F7" s="25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" ht="35.1" customHeight="1">
       <c r="A8" s="8"/>
       <c r="C8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" ht="35.1" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="24" t="s">
-        <v>217</v>
+        <v>96</v>
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" ht="35.1" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -17510,7 +17551,7 @@
       <c r="F10" s="16"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:32" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" ht="35.1" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -17519,7 +17560,7 @@
       <c r="F11" s="16"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -17528,7 +17569,7 @@
       <c r="F12" s="23"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -17537,7 +17578,7 @@
       <c r="F13" s="23"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -17546,7 +17587,7 @@
       <c r="F14" s="23"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -17555,7 +17596,7 @@
       <c r="F15" s="23"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -17564,7 +17605,7 @@
       <c r="F16" s="23"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -17572,7 +17613,7 @@
       <c r="E17" s="8"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -17580,7 +17621,7 @@
       <c r="E18" s="8"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -17588,7 +17629,7 @@
       <c r="E19" s="8"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -17596,7 +17637,7 @@
       <c r="E20" s="8"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -17604,7 +17645,7 @@
       <c r="E21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -17612,7 +17653,7 @@
       <c r="E22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -17620,7 +17661,7 @@
       <c r="E23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -17628,7 +17669,7 @@
       <c r="E24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -17636,7 +17677,7 @@
       <c r="E25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -17644,7 +17685,7 @@
       <c r="E26" s="8"/>
       <c r="G26" s="8"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -17652,7 +17693,7 @@
       <c r="E27" s="8"/>
       <c r="G27" s="8"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -17660,7 +17701,7 @@
       <c r="E28" s="8"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -17668,7 +17709,7 @@
       <c r="E29" s="8"/>
       <c r="G29" s="8"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -17676,7 +17717,7 @@
       <c r="E30" s="8"/>
       <c r="G30" s="8"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -17684,7 +17725,7 @@
       <c r="E31" s="8"/>
       <c r="G31" s="8"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
@@ -17692,203 +17733,203 @@
       <c r="E32"/>
       <c r="G32"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="E33" s="8"/>
       <c r="G33" s="8"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="E34" s="8"/>
       <c r="G34" s="8"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="E35" s="8"/>
       <c r="G35" s="8"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="E36" s="8"/>
       <c r="G36" s="8"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="E37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="E38" s="8"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="E39" s="8"/>
       <c r="G39" s="8"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="E40" s="8"/>
       <c r="G40" s="8"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="E41" s="8"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="E42" s="8"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="E43" s="8"/>
       <c r="G43" s="8"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="E44" s="8"/>
       <c r="G44" s="8"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="E45" s="8"/>
       <c r="G45" s="8"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="E46" s="8"/>
       <c r="G46" s="8"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="E47" s="8"/>
       <c r="G47" s="8"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="E48" s="8"/>
       <c r="G48" s="8"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="E49" s="8"/>
       <c r="G49" s="8"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="E50" s="8"/>
       <c r="G50" s="8"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="E51" s="8"/>
       <c r="G51" s="8"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="E52" s="8"/>
       <c r="G52" s="8"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="E53" s="8"/>
       <c r="G53" s="8"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="E54" s="8"/>
       <c r="G54" s="8"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="E55" s="8"/>
       <c r="G55" s="8"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="E56" s="8"/>
       <c r="G56" s="8"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="E57" s="8"/>
       <c r="G57" s="8"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="E58" s="8"/>
       <c r="G58" s="8"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="E59" s="8"/>
       <c r="G59" s="8"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="E60" s="8"/>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
